--- a/artfynd/A 16615-2020 artfynd.xlsx
+++ b/artfynd/A 16615-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126161</v>
+        <v>122126167</v>
       </c>
       <c r="B2" t="n">
         <v>56266</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487831</v>
+        <v>487836</v>
       </c>
       <c r="R2" t="n">
         <v>6282345</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,7 +819,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126167</v>
+        <v>122126161</v>
       </c>
       <c r="B3" t="n">
         <v>56266</v>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487836</v>
+        <v>487831</v>
       </c>
       <c r="R3" t="n">
         <v>6282345</v>
@@ -908,7 +908,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 16615-2020 artfynd.xlsx
+++ b/artfynd/A 16615-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126167</v>
+        <v>122126161</v>
       </c>
       <c r="B2" t="n">
         <v>56266</v>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487836</v>
+        <v>487831</v>
       </c>
       <c r="R2" t="n">
         <v>6282345</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,7 +819,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126161</v>
+        <v>122126167</v>
       </c>
       <c r="B3" t="n">
         <v>56266</v>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487831</v>
+        <v>487836</v>
       </c>
       <c r="R3" t="n">
         <v>6282345</v>
@@ -908,7 +908,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 16615-2020 artfynd.xlsx
+++ b/artfynd/A 16615-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126161</v>
+        <v>122126167</v>
       </c>
       <c r="B2" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487831</v>
+        <v>487836</v>
       </c>
       <c r="R2" t="n">
         <v>6282345</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,10 +819,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126167</v>
+        <v>122126161</v>
       </c>
       <c r="B3" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487836</v>
+        <v>487831</v>
       </c>
       <c r="R3" t="n">
         <v>6282345</v>
@@ -908,7 +908,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 16615-2020 artfynd.xlsx
+++ b/artfynd/A 16615-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126167</v>
+        <v>122126161</v>
       </c>
       <c r="B2" t="n">
         <v>56271</v>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>205998</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -729,7 +724,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487836</v>
+        <v>487831</v>
       </c>
       <c r="R2" t="n">
         <v>6282345</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,7 +814,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126161</v>
+        <v>122126167</v>
       </c>
       <c r="B3" t="n">
         <v>56271</v>
@@ -837,11 +832,6 @@
       <c r="E3" t="n">
         <v>205998</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -873,7 +863,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487831</v>
+        <v>487836</v>
       </c>
       <c r="R3" t="n">
         <v>6282345</v>
@@ -908,7 +898,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -918,7 +908,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 16615-2020 artfynd.xlsx
+++ b/artfynd/A 16615-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122126161</v>
+        <v>122126167</v>
       </c>
       <c r="B2" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>205998</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -724,7 +729,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487831</v>
+        <v>487836</v>
       </c>
       <c r="R2" t="n">
         <v>6282345</v>
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -814,10 +819,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122126167</v>
+        <v>122126161</v>
       </c>
       <c r="B3" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,6 +837,11 @@
       <c r="E3" t="n">
         <v>205998</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -863,7 +873,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487836</v>
+        <v>487831</v>
       </c>
       <c r="R3" t="n">
         <v>6282345</v>
@@ -898,7 +908,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -908,7 +918,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
